--- a/data/department_schedules_midterms/Makine Mühendisliği.xlsx
+++ b/data/department_schedules_midterms/Makine Mühendisliği.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/department_schedules_midterms/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_midterms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{BE5585BB-C03D-48D1-965B-D5E888A5DE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADF27CDC-197C-485C-8E8B-DE5D79D08E53}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0854E327-EB6A-497F-B7EC-8B40B51648CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17640" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30975" yWindow="11490" windowWidth="24465" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -472,15 +472,11 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{625B696F-FBE4-4EF2-8518-810C18A5AFBB}" name="Table1" displayName="Table1" ref="A1:F39" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
   <autoFilter ref="A1:F39" xr:uid="{625B696F-FBE4-4EF2-8518-810C18A5AFBB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F39">
-    <sortCondition ref="C1:C39"/>
+    <sortCondition ref="B1:B39"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{1FB3D1C1-309C-4BF7-AD72-258A5E23F6F0}" name="Year:" dataDxfId="5"/>
@@ -782,14 +778,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.9296875" customWidth="1"/>
-    <col min="5" max="5" width="33.265625" customWidth="1"/>
-    <col min="6" max="6" width="42.53125" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" customWidth="1"/>
+    <col min="5" max="5" width="33.26953125" customWidth="1"/>
+    <col min="6" max="6" width="42.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -809,752 +805,752 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>2</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3">
+        <v>4</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3">
+        <v>6</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>2</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3">
+        <v>8</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>3</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
-        <v>4</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4">
+        <v>4</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="5" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>3</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="4">
+        <v>5</v>
+      </c>
+      <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>3</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="4">
+        <v>8</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>3</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="4">
+        <v>7</v>
+      </c>
+      <c r="D16" s="4">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>3</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="4">
+        <v>3</v>
+      </c>
+      <c r="D17" s="4">
+        <v>3</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>3</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="4">
+        <v>4</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" s="5">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="5">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="5" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>3</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="4">
+        <v>4</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>3</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="4">
+        <v>4</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="5">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <v>4</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="5">
+        <v>4</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="5">
+        <v>4</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="5">
+        <v>7</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="5">
+        <v>4</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C23" s="5">
         <v>2</v>
       </c>
-      <c r="D7" s="5">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="D23" s="5">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="5">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="5">
+        <v>4</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C24" s="5">
         <v>2</v>
       </c>
-      <c r="D8" s="5">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="D24" s="5">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="5">
-        <v>4</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="5">
-        <v>2</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" s="5" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="5">
+        <v>4</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="5">
+        <v>5</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" s="5">
-        <v>4</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" s="2">
-        <v>1</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2">
-        <v>4</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" s="4">
-        <v>3</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="4">
-        <v>3</v>
-      </c>
-      <c r="D12" s="4">
-        <v>3</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" s="3">
-        <v>2</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="3">
-        <v>4</v>
-      </c>
-      <c r="D13" s="3">
-        <v>3</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" s="4">
-        <v>3</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="4">
-        <v>4</v>
-      </c>
-      <c r="D14" s="4">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="4" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="5">
+        <v>4</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="5">
+        <v>6</v>
+      </c>
+      <c r="D26" s="5">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15" s="4">
-        <v>3</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="4">
-        <v>4</v>
-      </c>
-      <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A16" s="4">
-        <v>3</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="4">
-        <v>4</v>
-      </c>
-      <c r="D16" s="4">
-        <v>1</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A17" s="5">
-        <v>4</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="5">
-        <v>4</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A18" s="5">
-        <v>4</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="5">
-        <v>4</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A19" s="5">
-        <v>4</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="5">
-        <v>4</v>
-      </c>
-      <c r="D19" s="5">
-        <v>1</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A20" s="2">
-        <v>1</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="2">
-        <v>5</v>
-      </c>
-      <c r="D20" s="2">
-        <v>3</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A21" s="3">
-        <v>2</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="3">
-        <v>5</v>
-      </c>
-      <c r="D21" s="3">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A22" s="4">
-        <v>3</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="4">
-        <v>5</v>
-      </c>
-      <c r="D22" s="4">
-        <v>3</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A23" s="5">
-        <v>4</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="5">
-        <v>5</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" s="5">
-        <v>4</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="5">
-        <v>5</v>
-      </c>
-      <c r="D24" s="5">
-        <v>1</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A25" s="2">
-        <v>1</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="2">
-        <v>6</v>
-      </c>
-      <c r="D25" s="2">
-        <v>3</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A26" s="3">
-        <v>2</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="3">
-        <v>6</v>
-      </c>
-      <c r="D26" s="3">
-        <v>3</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>4</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C27" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" s="5">
         <v>1</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>4</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D28" s="5">
         <v>1</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A29" s="2">
-        <v>1</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="5">
+        <v>4</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="5">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="5">
+        <v>4</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="5">
         <v>7</v>
       </c>
-      <c r="D29" s="2">
-        <v>3</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A30" s="3">
+      <c r="D30" s="5">
+        <v>1</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="5">
+        <v>4</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="5">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="5">
+        <v>4</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="5">
         <v>2</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="3">
-        <v>7</v>
-      </c>
-      <c r="D30" s="3">
-        <v>3</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A31" s="4">
-        <v>3</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" s="4">
-        <v>7</v>
-      </c>
-      <c r="D31" s="4">
-        <v>3</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A32" s="5">
-        <v>4</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="5">
-        <v>7</v>
-      </c>
       <c r="D32" s="5">
         <v>1</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>4</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C33" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D33" s="5">
         <v>1</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>4</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C34" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34" s="5">
         <v>1</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A35" s="2">
-        <v>1</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="5">
+        <v>4</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="5">
         <v>8</v>
       </c>
-      <c r="D35" s="2">
-        <v>3</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A36" s="3">
-        <v>2</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="3">
-        <v>8</v>
-      </c>
-      <c r="D36" s="3">
-        <v>2</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A37" s="4">
-        <v>3</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C37" s="4">
-        <v>8</v>
-      </c>
-      <c r="D37" s="4">
-        <v>2</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A38" s="5">
-        <v>4</v>
-      </c>
-      <c r="B38" s="5" t="s">
+      <c r="D35" s="5">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="5">
+        <v>4</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="5">
+        <v>4</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="5">
+        <v>4</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="5">
+        <v>5</v>
+      </c>
+      <c r="D37" s="5">
+        <v>1</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
+        <v>1</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="2">
+        <v>5</v>
+      </c>
+      <c r="D38" s="2">
+        <v>3</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="5">
+        <v>4</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="C38" s="5">
-        <v>8</v>
-      </c>
-      <c r="D38" s="5">
-        <v>1</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A39" s="5">
-        <v>4</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="C39" s="5">
         <v>8</v>
@@ -1563,10 +1559,10 @@
         <v>1</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
